--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -1547,7 +1547,7 @@
         <v>136444139</v>
       </c>
       <c r="B9" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -1547,7 +1547,7 @@
         <v>136444139</v>
       </c>
       <c r="B9" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>136443683</v>
       </c>
       <c r="B4" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136444139</v>
       </c>
       <c r="B9" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -1547,7 +1547,7 @@
         <v>136444139</v>
       </c>
       <c r="B9" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -1547,7 +1547,7 @@
         <v>136444139</v>
       </c>
       <c r="B9" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -1547,7 +1547,7 @@
         <v>136444139</v>
       </c>
       <c r="B9" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -1547,7 +1547,7 @@
         <v>136444139</v>
       </c>
       <c r="B9" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
